--- a/artfynd/A 16537-2025 artfynd.xlsx
+++ b/artfynd/A 16537-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125110076</v>
+        <v>125110077</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>879683</v>
+        <v>879609</v>
       </c>
       <c r="R2" t="n">
-        <v>7378165</v>
+        <v>7378310</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125110077</v>
+        <v>125110076</v>
       </c>
       <c r="B3" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>879609</v>
+        <v>879683</v>
       </c>
       <c r="R3" t="n">
-        <v>7378310</v>
+        <v>7378165</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 16537-2025 artfynd.xlsx
+++ b/artfynd/A 16537-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125110077</v>
+        <v>125110076</v>
       </c>
       <c r="B2" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>879609</v>
+        <v>879683</v>
       </c>
       <c r="R2" t="n">
-        <v>7378310</v>
+        <v>7378165</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125110076</v>
+        <v>125110077</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>879683</v>
+        <v>879609</v>
       </c>
       <c r="R3" t="n">
-        <v>7378165</v>
+        <v>7378310</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 16537-2025 artfynd.xlsx
+++ b/artfynd/A 16537-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125110077</v>
       </c>
       <c r="B2" t="n">
-        <v>56722</v>
+        <v>56836</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>125110076</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 16537-2025 artfynd.xlsx
+++ b/artfynd/A 16537-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125110077</v>
+        <v>125110076</v>
       </c>
       <c r="B2" t="n">
-        <v>56836</v>
+        <v>57635</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>879609</v>
+        <v>879683</v>
       </c>
       <c r="R2" t="n">
-        <v>7378310</v>
+        <v>7378165</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125110076</v>
+        <v>125110077</v>
       </c>
       <c r="B3" t="n">
-        <v>57635</v>
+        <v>56836</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>879683</v>
+        <v>879609</v>
       </c>
       <c r="R3" t="n">
-        <v>7378165</v>
+        <v>7378310</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 16537-2025 artfynd.xlsx
+++ b/artfynd/A 16537-2025 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125110076</v>
+        <v>125110077</v>
       </c>
       <c r="B2" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56843</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>879683</v>
+        <v>879609</v>
       </c>
       <c r="R2" t="n">
-        <v>7378165</v>
+        <v>7378310</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,37 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125110077</v>
+        <v>125110076</v>
       </c>
       <c r="B3" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>879609</v>
+        <v>879683</v>
       </c>
       <c r="R3" t="n">
-        <v>7378310</v>
+        <v>7378165</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -862,7 +852,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 16537-2025 artfynd.xlsx
+++ b/artfynd/A 16537-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125110077</v>
       </c>
       <c r="B2" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 16537-2025 artfynd.xlsx
+++ b/artfynd/A 16537-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125110077</v>
       </c>
       <c r="B2" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 16537-2025 artfynd.xlsx
+++ b/artfynd/A 16537-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125110077</v>
       </c>
       <c r="B2" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson, Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 16537-2025 artfynd.xlsx
+++ b/artfynd/A 16537-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125110077</v>
       </c>
       <c r="B2" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Marie Persson, Viktoria Sturk</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
